--- a/data/forecasts/opex-nov-2025-forecast.xlsx
+++ b/data/forecasts/opex-nov-2025-forecast.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dan.jellesma/python/costvsforecast/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dan.jellesma/python/streamdeck/data/forecasts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81A14356-06D6-5C4B-A3FF-117F9660725F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9773FBF1-5254-D242-8B71-25D4D1B021DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20980" yWindow="7580" windowWidth="26840" windowHeight="15940" xr2:uid="{7243C9BD-8627-204F-BEBD-14D2F38BCC96}"/>
+    <workbookView xWindow="11140" yWindow="5340" windowWidth="26840" windowHeight="15940" xr2:uid="{7243C9BD-8627-204F-BEBD-14D2F38BCC96}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>AWS Enterprise Support</t>
   </si>
@@ -84,6 +84,42 @@
   </si>
   <si>
     <t>Apr-2026</t>
+  </si>
+  <si>
+    <t>May-2026</t>
+  </si>
+  <si>
+    <t>Jun-2026</t>
+  </si>
+  <si>
+    <t>Jul-2026</t>
+  </si>
+  <si>
+    <t>Aug-2026</t>
+  </si>
+  <si>
+    <t>Sep-2026</t>
+  </si>
+  <si>
+    <t>Oct-2026</t>
+  </si>
+  <si>
+    <t>Nov-2026</t>
+  </si>
+  <si>
+    <t>Dec-2026</t>
+  </si>
+  <si>
+    <t>Jan-2027</t>
+  </si>
+  <si>
+    <t>Feb-2027</t>
+  </si>
+  <si>
+    <t>Mar-2027</t>
+  </si>
+  <si>
+    <t>Apr-2027</t>
   </si>
 </sst>
 </file>
@@ -455,10 +491,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90008498-374D-B044-A273-B2BC2E1018C6}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,8 +516,44 @@
       <c r="G1" t="s">
         <v>15</v>
       </c>
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -503,8 +575,44 @@
       <c r="G2">
         <v>230093.9323742144</v>
       </c>
+      <c r="H2">
+        <v>248609.31765309852</v>
+      </c>
+      <c r="I2">
+        <v>242995.55886738337</v>
+      </c>
+      <c r="J2">
+        <v>253606.3649379258</v>
+      </c>
+      <c r="K2">
+        <v>256142.42858730507</v>
+      </c>
+      <c r="L2">
+        <v>250358.56729662401</v>
+      </c>
+      <c r="M2">
+        <v>261290.89140190993</v>
+      </c>
+      <c r="N2">
+        <v>255390.77449928617</v>
+      </c>
+      <c r="O2">
+        <v>266542.83831908833</v>
+      </c>
+      <c r="P2">
+        <v>269208.26670227922</v>
+      </c>
+      <c r="Q2">
+        <v>245587.41233356312</v>
+      </c>
+      <c r="R2">
+        <v>274619.35286299506</v>
+      </c>
+      <c r="S2">
+        <v>268418.27070157259</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -526,8 +634,44 @@
       <c r="G3">
         <v>344515.53981143452</v>
       </c>
+      <c r="H3">
+        <v>349830.16223457019</v>
+      </c>
+      <c r="I3">
+        <v>333163.31579560315</v>
+      </c>
+      <c r="J3">
+        <v>347711.44725201104</v>
+      </c>
+      <c r="K3">
+        <v>343795.11831980431</v>
+      </c>
+      <c r="L3">
+        <v>334225.37907416985</v>
+      </c>
+      <c r="M3">
+        <v>320537.19372938445</v>
+      </c>
+      <c r="N3">
+        <v>313299.25709678541</v>
+      </c>
+      <c r="O3">
+        <v>317362.93275501131</v>
+      </c>
+      <c r="P3">
+        <v>310823.33292854443</v>
+      </c>
+      <c r="Q3">
+        <v>265829.14884735603</v>
+      </c>
+      <c r="R3">
+        <v>297253.95180038264</v>
+      </c>
+      <c r="S3">
+        <v>290541.76579198701</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -549,8 +693,44 @@
       <c r="G4">
         <v>172482.74368430427</v>
       </c>
+      <c r="H4">
+        <v>199268.35644266329</v>
+      </c>
+      <c r="I4">
+        <v>194768.74839395803</v>
+      </c>
+      <c r="J4">
+        <v>203273.65040716081</v>
+      </c>
+      <c r="K4">
+        <v>205306.38691123249</v>
+      </c>
+      <c r="L4">
+        <v>200670.43623904337</v>
+      </c>
+      <c r="M4">
+        <v>209433.04528814828</v>
+      </c>
+      <c r="N4">
+        <v>204703.91200744809</v>
+      </c>
+      <c r="O4">
+        <v>213642.64949844003</v>
+      </c>
+      <c r="P4">
+        <v>215779.07599342443</v>
+      </c>
+      <c r="Q4">
+        <v>196846.20222884009</v>
+      </c>
+      <c r="R4">
+        <v>220116.23542089222</v>
+      </c>
+      <c r="S4">
+        <v>215145.86881461408</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -572,8 +752,44 @@
       <c r="G5">
         <v>118571.21731007031</v>
       </c>
+      <c r="H5">
+        <v>112827.59674347854</v>
+      </c>
+      <c r="I5">
+        <v>107452.18766785873</v>
+      </c>
+      <c r="J5">
+        <v>112144.2665293552</v>
+      </c>
+      <c r="K5">
+        <v>110881.16794844567</v>
+      </c>
+      <c r="L5">
+        <v>107794.72544831983</v>
+      </c>
+      <c r="M5">
+        <v>103379.99732320217</v>
+      </c>
+      <c r="N5">
+        <v>101045.61028687176</v>
+      </c>
+      <c r="O5">
+        <v>102356.23129088679</v>
+      </c>
+      <c r="P5">
+        <v>100247.07258549884</v>
+      </c>
+      <c r="Q5">
+        <v>85735.500384614134</v>
+      </c>
+      <c r="R5">
+        <v>95870.661322938133</v>
+      </c>
+      <c r="S5">
+        <v>93705.839938226651</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -595,8 +811,44 @@
       <c r="G6">
         <v>544.08920694644974</v>
       </c>
+      <c r="H6">
+        <v>875.05136194206489</v>
+      </c>
+      <c r="I6">
+        <v>855.29213764014742</v>
+      </c>
+      <c r="J6">
+        <v>892.63989431710024</v>
+      </c>
+      <c r="K6">
+        <v>901.56629326027155</v>
+      </c>
+      <c r="L6">
+        <v>881.20834470278157</v>
+      </c>
+      <c r="M6">
+        <v>919.68777575480306</v>
+      </c>
+      <c r="N6">
+        <v>898.92063243130724</v>
+      </c>
+      <c r="O6">
+        <v>938.17350004747448</v>
+      </c>
+      <c r="P6">
+        <v>947.55523504794928</v>
+      </c>
+      <c r="Q6">
+        <v>864.41490474696798</v>
+      </c>
+      <c r="R6">
+        <v>966.60109527241286</v>
+      </c>
+      <c r="S6">
+        <v>944.77461892755218</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -618,8 +870,44 @@
       <c r="G7">
         <v>34668.70063868595</v>
       </c>
+      <c r="H7">
+        <v>37112.906848929728</v>
+      </c>
+      <c r="I7">
+        <v>36274.873468470032</v>
+      </c>
+      <c r="J7">
+        <v>37858.876276593212</v>
+      </c>
+      <c r="K7">
+        <v>38237.465039359151</v>
+      </c>
+      <c r="L7">
+        <v>37374.038409438144</v>
+      </c>
+      <c r="M7">
+        <v>39006.038086650275</v>
+      </c>
+      <c r="N7">
+        <v>38125.256581467846</v>
+      </c>
+      <c r="O7">
+        <v>39790.059452191941</v>
+      </c>
+      <c r="P7">
+        <v>40187.960046713859</v>
+      </c>
+      <c r="Q7">
+        <v>36661.790649066716</v>
+      </c>
+      <c r="R7">
+        <v>40995.738043652804</v>
+      </c>
+      <c r="S7">
+        <v>40070.02782976388</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -641,8 +929,44 @@
       <c r="G8">
         <v>116280.21753188585</v>
       </c>
+      <c r="H8">
+        <v>92972.126708414682</v>
+      </c>
+      <c r="I8">
+        <v>90872.756105321474</v>
+      </c>
+      <c r="J8">
+        <v>94840.86645525381</v>
+      </c>
+      <c r="K8">
+        <v>95789.275119806378</v>
+      </c>
+      <c r="L8">
+        <v>93626.291488068819</v>
+      </c>
+      <c r="M8">
+        <v>97714.639549714499</v>
+      </c>
+      <c r="N8">
+        <v>95508.179946978984</v>
+      </c>
+      <c r="O8">
+        <v>99678.703804663746</v>
+      </c>
+      <c r="P8">
+        <v>100675.49084271038</v>
+      </c>
+      <c r="Q8">
+        <v>91842.028420382267</v>
+      </c>
+      <c r="R8">
+        <v>102699.06820864884</v>
+      </c>
+      <c r="S8">
+        <v>100380.05699103423</v>
+      </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -664,8 +988,44 @@
       <c r="G9">
         <v>83570.873277361417</v>
       </c>
+      <c r="H9">
+        <v>68331.17271399952</v>
+      </c>
+      <c r="I9">
+        <v>66788.210749489866</v>
+      </c>
+      <c r="J9">
+        <v>69704.629285550909</v>
+      </c>
+      <c r="K9">
+        <v>70401.675578406444</v>
+      </c>
+      <c r="L9">
+        <v>68811.960323410167</v>
+      </c>
+      <c r="M9">
+        <v>71816.749257532414</v>
+      </c>
+      <c r="N9">
+        <v>70195.080725910695</v>
+      </c>
+      <c r="O9">
+        <v>73260.265917608805</v>
+      </c>
+      <c r="P9">
+        <v>73992.868576784895</v>
+      </c>
+      <c r="Q9">
+        <v>67500.591075854099</v>
+      </c>
+      <c r="R9">
+        <v>75480.12523517826</v>
+      </c>
+      <c r="S9">
+        <v>73775.735310512959</v>
+      </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -687,8 +1047,44 @@
       <c r="G10">
         <v>94179.519667297165</v>
       </c>
+      <c r="H10">
+        <v>63398.547254571997</v>
+      </c>
+      <c r="I10">
+        <v>63095.999413339727</v>
+      </c>
+      <c r="J10">
+        <v>63667.858054388889</v>
+      </c>
+      <c r="K10">
+        <v>63804.536634932781</v>
+      </c>
+      <c r="L10">
+        <v>63492.821291563334</v>
+      </c>
+      <c r="M10">
+        <v>64082.00782129493</v>
+      </c>
+      <c r="N10">
+        <v>63764.026999523754</v>
+      </c>
+      <c r="O10">
+        <v>64365.056178502957</v>
+      </c>
+      <c r="P10">
+        <v>64508.706740287991</v>
+      </c>
+      <c r="Q10">
+        <v>63235.684729527238</v>
+      </c>
+      <c r="R10">
+        <v>64800.331745767777</v>
+      </c>
+      <c r="S10">
+        <v>64466.13070634722</v>
+      </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>179134.84769273625</v>
       </c>
@@ -706,6 +1102,42 @@
       </c>
       <c r="G11">
         <v>188272.52524819862</v>
+      </c>
+      <c r="H11">
+        <v>202300.0561411861</v>
+      </c>
+      <c r="I11">
+        <v>197731.99035735289</v>
+      </c>
+      <c r="J11">
+        <v>206366.28726962389</v>
+      </c>
+      <c r="K11">
+        <v>208429.95014232022</v>
+      </c>
+      <c r="L11">
+        <v>203723.46739717104</v>
+      </c>
+      <c r="M11">
+        <v>212619.39214018086</v>
+      </c>
+      <c r="N11">
+        <v>207818.30909185414</v>
+      </c>
+      <c r="O11">
+        <v>216893.04192219846</v>
+      </c>
+      <c r="P11">
+        <v>219061.97234142045</v>
+      </c>
+      <c r="Q11">
+        <v>199841.05089727003</v>
+      </c>
+      <c r="R11">
+        <v>223465.11798548297</v>
+      </c>
+      <c r="S11">
+        <v>218419.13145032697</v>
       </c>
     </row>
   </sheetData>
